--- a/Courses_Data.xlsx
+++ b/Courses_Data.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonipieszczoch/Desktop/Optimised Math Learning/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6065C5D3-7D5D-2F4D-9870-B168B9BDAAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{403890A9-C917-BC41-96EF-6BB1034E316E}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Courses_Data"/>
+    <sheet name="Courses_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>Macro_Topic</t>
   </si>
@@ -73,18 +79,24 @@
     <t>Calculate by multiplying the numerators instead of adding them, using the correct scaled denominator.</t>
   </si>
   <si>
+    <t>add_fractions_single_conversion</t>
+  </si>
+  <si>
     <t>Double Conversion</t>
   </si>
   <si>
     <t>Denominators are coprime (e.g., 3 &amp; 4). Requires mutual multiplication. Constraint: Final sum must not be simplifiable.</t>
   </si>
   <si>
-    <t>Calculate by adding numerator to numerator and denominator to denominator directly.</t>
+    <t>Calculate by adding numerator to numerator and multiplying the denominators directly.</t>
   </si>
   <si>
     <t>Calculate using the correct common denominator, but fail to multiply the numerators by their respective scaling factors.</t>
   </si>
   <si>
+    <t>add_fractions_complex</t>
+  </si>
+  <si>
     <t>Mixed Numbers (Easy)</t>
   </si>
   <si>
@@ -97,6 +109,9 @@
     <t>Calculate by converting to improper fractions, but make a +/- 1 arithmetic error in the final numerator addition.</t>
   </si>
   <si>
+    <t>add_mixed_numbers_simple</t>
+  </si>
+  <si>
     <t>The Final Boss</t>
   </si>
   <si>
@@ -107,37 +122,333 @@
   </si>
   <si>
     <t>Calculate by finding the common denominator, but adding the original unscaled numerators together.</t>
+  </si>
+  <si>
+    <t>add_mixed_numbers_complex</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -149,51 +460,209 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -204,10 +673,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -234,82 +703,116 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -321,342 +824,327 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081EDEFC-3A96-B142-AFD4-AFCA554E65C7}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="20.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="53.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="33.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="18.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25" customFormat="1" s="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="51">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="51">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="51">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="51">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="51">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>14</v>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Courses_Data.xlsx
+++ b/Courses_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonipieszczoch/Desktop/Optimised Math Learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6065C5D3-7D5D-2F4D-9870-B168B9BDAAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F4C6614-F7D1-0143-8377-BB391264A977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{403890A9-C917-BC41-96EF-6BB1034E316E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{F53E98A7-EF1E-924B-8C9E-487A44BE2458}"/>
   </bookViews>
   <sheets>
     <sheet name="Courses_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>Macro_Topic</t>
   </si>
@@ -46,31 +46,40 @@
     <t>Function_Name</t>
   </si>
   <si>
+    <t>Trap_Message</t>
+  </si>
+  <si>
+    <t>Wrong_Message</t>
+  </si>
+  <si>
     <t>Fractions</t>
   </si>
   <si>
-    <t>Addition and Substraction</t>
+    <t>Addition</t>
   </si>
   <si>
     <t>Identical Denominators</t>
   </si>
   <si>
-    <t>Denominators must match. Numerators 1-9. Sum must be less than denominator. Constraint: Final sum must not be simplifiable (e.g., avoid 2/4 or 4/4). Output the raw fraction.</t>
+    <t>Denominators must match. Numerators 1-9. Sum must be less than denominator. Constraint: Final sum must not be simplifiable.</t>
   </si>
   <si>
     <t>Calculate by adding numerator A to numerator B, AND adding denominator A to denominator B. Format as a/b.</t>
   </si>
   <si>
-    <t>Calculate by making a +/- 1 arithmetic error in the correct numerator sum. Keep the denominator correct.</t>
+    <t>Calculate by making a +/- 1 arithmetic error in the correct numerator sum.</t>
   </si>
   <si>
     <t>add_fractions_simple</t>
   </si>
   <si>
+    <t>Niezupełnie. To jest zwykły błąd obliczeniowy w liczniku. Spróbuj jeszcze raz!</t>
+  </si>
+  <si>
     <t>Single Conversion</t>
   </si>
   <si>
-    <t>Denominators differ. One is a direct multiple of the other (e.g., 2 &amp; 4). Constraint:Final sum must not be simplifiable.</t>
+    <t>Denominators differ. One is a direct multiple of the other.</t>
   </si>
   <si>
     <t>Calculate by adding the unscaled numerator of fraction A to the numerator of fraction B, placing the sum over the larger denominator.</t>
@@ -82,13 +91,19 @@
     <t>add_fractions_single_conversion</t>
   </si>
   <si>
+    <t>Dodałeś liczniki bez uprzedniego rozszerzenia ułamka!</t>
+  </si>
+  <si>
+    <t>Pomnożyłeś liczniki zamiast je dodać!</t>
+  </si>
+  <si>
     <t>Double Conversion</t>
   </si>
   <si>
-    <t>Denominators are coprime (e.g., 3 &amp; 4). Requires mutual multiplication. Constraint: Final sum must not be simplifiable.</t>
-  </si>
-  <si>
-    <t>Calculate by adding numerator to numerator and multiplying the denominators directly.</t>
+    <t>Denominators are coprime. Requires mutual multiplication.</t>
+  </si>
+  <si>
+    <t>Calculate by adding numerator to numerator and denominator to denominator directly.</t>
   </si>
   <si>
     <t>Calculate using the correct common denominator, but fail to multiply the numerators by their respective scaling factors.</t>
@@ -97,10 +112,16 @@
     <t>add_fractions_complex</t>
   </si>
   <si>
+    <t>Błąd! Dodałeś do siebie liczniki i mianowniki.</t>
+  </si>
+  <si>
+    <t>Znalazłeś wspólny mianownik, ale zapomniałeś rozszerzyć liczniki!</t>
+  </si>
+  <si>
     <t>Mixed Numbers (Easy)</t>
   </si>
   <si>
-    <t>Whole numbers included. Denominators are identical or require Single Conversion. Constraint: The fractional sum must not exceed 1.</t>
+    <t>Whole numbers included. Identical Denominators.</t>
   </si>
   <si>
     <t>Calculate by adding the whole numbers correctly, but applying the Level 1 trap (adding denominators) to the fractional part.</t>
@@ -112,19 +133,34 @@
     <t>add_mixed_numbers_simple</t>
   </si>
   <si>
+    <t>Całości dodane świetnie, ale mianowniki ułamków również zostały dodane. Mianownik musi zostać bez zmian!</t>
+  </si>
+  <si>
+    <t>Pojawił się błąd obliczeniowy podczas dodawania liczników.</t>
+  </si>
+  <si>
     <t>The Final Boss</t>
   </si>
   <si>
-    <t>Mixed numbers. Denominators are coprime. Constraint: Sum of the fractions must exceed 1 (requires carrying over to the whole number).</t>
-  </si>
-  <si>
-    <t>Calculate by leaving the fractional part as an improper fraction and failing to carry the 1 over to the whole number sum.</t>
+    <t>Mixed numbers. Denominators are coprime.</t>
   </si>
   <si>
     <t>Calculate by finding the common denominator, but adding the original unscaled numerators together.</t>
   </si>
   <si>
+    <t>Calculate by adding the whole numbers, adding the numerators, and adding the denominators.</t>
+  </si>
+  <si>
     <t>add_mixed_numbers_complex</t>
+  </si>
+  <si>
+    <t>Zapomniałeś rozszerzyć liczniki przed dodaniem ułamków!</t>
+  </si>
+  <si>
+    <t>Błąd! Dodałeś do siebie mianowniki.</t>
+  </si>
+  <si>
+    <t>Dodałeś mianowniki. W dodawaniu ułamków mianownik zostaje bez zmian.</t>
   </si>
 </sst>
 </file>
@@ -984,11 +1020,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081EDEFC-3A96-B142-AFD4-AFCA554E65C7}">
-  <dimension ref="A1:H6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4696064F-12C5-9F40-B02D-0B74D749CBBB}">
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1013,135 +1049,171 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
